--- a/ig/DM-37/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="167">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -500,6 +500,21 @@
   </si>
   <si>
     <t>Feuille de style</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:dlu:2024</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:ft-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
+    <t>urn:asip:ci-sis:fr-su:2024</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
   </si>
 </sst>
 </file>
@@ -873,7 +888,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D60"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1617,42 @@
       </c>
       <c r="D60" s="2"/>
     </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="D61" s="2"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="D62" s="2"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C63" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="D63" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
